--- a/output/graficos_dimensiones/comunal_e_basbrut_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basbrut_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 00:32</t>
+    <t xml:space="preserve">2026-08-17 15:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_basbrut_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basbrut_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 15:26</t>
+    <t xml:space="preserve">2026-08-17 20:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_basbrut_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basbrut_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 20:19</t>
+    <t xml:space="preserve">2026-09-06 21:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
